--- a/李源德组/电赛/采样板ADC标定.xlsx
+++ b/李源德组/电赛/采样板ADC标定.xlsx
@@ -8,15 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\张辉宇\Desktop\Our Preparation\李源德组\电赛\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{5E49D8E5-19C3-4751-93BD-6B3465470080}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5100CD1A-EDEF-4041-BB57-7B0A48A4D8D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12710" yWindow="0" windowWidth="12980" windowHeight="15370" xr2:uid="{8995212B-BAD0-47B4-B21B-AD3EB2433BD5}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{8995212B-BAD0-47B4-B21B-AD3EB2433BD5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="15">
   <si>
     <t>万用表</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -485,7 +484,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30C42203-CB11-46C3-8692-3B3A8456F224}">
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:L26"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="5" max="5" width="11.33203125" customWidth="1"/>
@@ -493,15 +492,12 @@
     <col min="7" max="7" width="9.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:12">
       <c r="A1" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="B1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E1" t="s">
         <v>8</v>
@@ -518,16 +514,22 @@
       <c r="I1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:9">
+      <c r="J1" t="s">
+        <v>2</v>
+      </c>
+      <c r="K1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
       <c r="A2">
-        <v>0</v>
+        <v>2046</v>
       </c>
       <c r="B2">
-        <v>0</v>
-      </c>
-      <c r="C2">
-        <v>0</v>
+        <v>2046</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -544,16 +546,22 @@
       <c r="I2">
         <v>2175</v>
       </c>
-    </row>
-    <row r="3" spans="1:9">
+      <c r="J2">
+        <v>2046</v>
+      </c>
+      <c r="K2">
+        <v>1951</v>
+      </c>
+      <c r="L2">
+        <v>2159</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
       <c r="A3">
-        <v>4</v>
+        <v>2046</v>
       </c>
       <c r="B3">
-        <v>4</v>
-      </c>
-      <c r="C3">
-        <v>187</v>
+        <v>2046</v>
       </c>
       <c r="E3">
         <v>5</v>
@@ -570,16 +578,22 @@
       <c r="I3">
         <v>2375</v>
       </c>
-    </row>
-    <row r="4" spans="1:9">
+      <c r="J3">
+        <v>2048</v>
+      </c>
+      <c r="K3">
+        <v>1703</v>
+      </c>
+      <c r="L3">
+        <v>2367</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
       <c r="A4">
-        <v>8</v>
+        <v>2046</v>
       </c>
       <c r="B4">
-        <v>7.99</v>
-      </c>
-      <c r="C4">
-        <v>377</v>
+        <v>2046</v>
       </c>
       <c r="E4">
         <v>10</v>
@@ -596,16 +610,22 @@
       <c r="I4">
         <v>2612</v>
       </c>
-    </row>
-    <row r="5" spans="1:9">
+      <c r="J4">
+        <v>2050</v>
+      </c>
+      <c r="K4">
+        <v>1467</v>
+      </c>
+      <c r="L4">
+        <v>2613</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
       <c r="A5">
-        <v>12</v>
+        <v>2046</v>
       </c>
       <c r="B5">
-        <v>11.99</v>
-      </c>
-      <c r="C5">
-        <v>568</v>
+        <v>2046</v>
       </c>
       <c r="E5">
         <v>20</v>
@@ -622,16 +642,22 @@
       <c r="I5">
         <v>3151</v>
       </c>
-    </row>
-    <row r="6" spans="1:9">
+      <c r="J5">
+        <v>2049</v>
+      </c>
+      <c r="K5">
+        <v>927</v>
+      </c>
+      <c r="L5">
+        <v>3188</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
       <c r="A6">
-        <v>16</v>
+        <v>2046</v>
       </c>
       <c r="B6">
-        <v>15.99</v>
-      </c>
-      <c r="C6">
-        <v>759</v>
+        <v>2046</v>
       </c>
       <c r="E6">
         <v>24</v>
@@ -648,16 +674,22 @@
       <c r="I6">
         <v>3353</v>
       </c>
-    </row>
-    <row r="7" spans="1:9">
+      <c r="J6">
+        <v>2050</v>
+      </c>
+      <c r="K6">
+        <v>818</v>
+      </c>
+      <c r="L6">
+        <v>3328</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
       <c r="A7">
-        <v>20</v>
+        <v>2046</v>
       </c>
       <c r="B7">
-        <v>19.989999999999998</v>
-      </c>
-      <c r="C7">
-        <v>952</v>
+        <v>2046</v>
       </c>
       <c r="E7">
         <v>28</v>
@@ -674,16 +706,22 @@
       <c r="I7">
         <v>3477</v>
       </c>
-    </row>
-    <row r="8" spans="1:9">
+      <c r="J7">
+        <v>2049</v>
+      </c>
+      <c r="K7">
+        <v>555</v>
+      </c>
+      <c r="L7">
+        <v>3524</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
       <c r="A8">
-        <v>24</v>
+        <v>2046</v>
       </c>
       <c r="B8">
-        <v>23.99</v>
-      </c>
-      <c r="C8">
-        <v>1144</v>
+        <v>2046</v>
       </c>
       <c r="E8">
         <v>32</v>
@@ -700,16 +738,22 @@
       <c r="I8">
         <v>3712</v>
       </c>
-    </row>
-    <row r="9" spans="1:9">
+      <c r="J8">
+        <v>2049</v>
+      </c>
+      <c r="K8">
+        <v>447</v>
+      </c>
+      <c r="L8">
+        <v>3712</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
       <c r="A9">
-        <v>28</v>
+        <v>2046</v>
       </c>
       <c r="B9">
-        <v>27.99</v>
-      </c>
-      <c r="C9">
-        <v>1340</v>
+        <v>2046</v>
       </c>
       <c r="E9">
         <v>36</v>
@@ -726,16 +770,22 @@
       <c r="I9">
         <v>3919</v>
       </c>
-    </row>
-    <row r="10" spans="1:9">
+      <c r="J9">
+        <v>2048</v>
+      </c>
+      <c r="K9">
+        <v>149</v>
+      </c>
+      <c r="L9">
+        <v>3913</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
       <c r="A10">
-        <v>31</v>
+        <v>2046</v>
       </c>
       <c r="B10">
-        <v>30.99</v>
-      </c>
-      <c r="C10">
-        <v>1483</v>
+        <v>2046</v>
       </c>
       <c r="E10">
         <v>37.5</v>
@@ -752,14 +802,25 @@
       <c r="I10">
         <v>3981</v>
       </c>
-    </row>
-    <row r="12" spans="1:9">
-      <c r="A12" t="s">
-        <v>6</v>
-      </c>
-      <c r="B12" t="s">
-        <v>7</v>
-      </c>
+      <c r="J10">
+        <v>2043</v>
+      </c>
+      <c r="K10">
+        <v>126</v>
+      </c>
+      <c r="L10">
+        <v>3968</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="A11">
+        <v>2046</v>
+      </c>
+      <c r="B11">
+        <v>2046</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
       <c r="E12" t="s">
         <v>9</v>
       </c>
@@ -775,13 +836,25 @@
       <c r="I12" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="13" spans="1:9">
-      <c r="A13">
-        <v>2046</v>
-      </c>
-      <c r="B13">
-        <v>2046</v>
+      <c r="J12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" t="s">
+        <v>0</v>
+      </c>
+      <c r="C13" t="s">
+        <v>1</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -799,12 +872,15 @@
         <v>2074</v>
       </c>
     </row>
-    <row r="14" spans="1:9">
+    <row r="14" spans="1:12">
       <c r="A14">
-        <v>2046</v>
+        <v>0</v>
       </c>
       <c r="B14">
-        <v>2046</v>
+        <v>0</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
       </c>
       <c r="E14">
         <v>0.2</v>
@@ -821,13 +897,25 @@
       <c r="I14">
         <v>2221</v>
       </c>
-    </row>
-    <row r="15" spans="1:9">
+      <c r="J14">
+        <v>2055</v>
+      </c>
+      <c r="K14">
+        <v>1919</v>
+      </c>
+      <c r="L14">
+        <v>2201</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
       <c r="A15">
-        <v>2046</v>
+        <v>4</v>
       </c>
       <c r="B15">
-        <v>2046</v>
+        <v>4</v>
+      </c>
+      <c r="C15">
+        <v>187</v>
       </c>
       <c r="E15">
         <v>0.5</v>
@@ -844,13 +932,25 @@
       <c r="I15">
         <v>2351</v>
       </c>
-    </row>
-    <row r="16" spans="1:9">
+      <c r="J15">
+        <v>2062</v>
+      </c>
+      <c r="K15">
+        <v>1791</v>
+      </c>
+      <c r="L15">
+        <v>2335</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
       <c r="A16">
-        <v>2046</v>
+        <v>8</v>
       </c>
       <c r="B16">
-        <v>2046</v>
+        <v>7.99</v>
+      </c>
+      <c r="C16">
+        <v>377</v>
       </c>
       <c r="E16">
         <v>1</v>
@@ -867,13 +967,25 @@
       <c r="I16">
         <v>2557</v>
       </c>
-    </row>
-    <row r="17" spans="1:9">
+      <c r="J16">
+        <v>2064</v>
+      </c>
+      <c r="K16">
+        <v>1599</v>
+      </c>
+      <c r="L16">
+        <v>2560</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12">
       <c r="A17">
-        <v>2046</v>
+        <v>12</v>
       </c>
       <c r="B17">
-        <v>2046</v>
+        <v>11.99</v>
+      </c>
+      <c r="C17">
+        <v>566</v>
       </c>
       <c r="E17">
         <v>1.5</v>
@@ -890,13 +1002,25 @@
       <c r="I17">
         <v>2742</v>
       </c>
-    </row>
-    <row r="18" spans="1:9">
+      <c r="J17">
+        <v>2064</v>
+      </c>
+      <c r="K17">
+        <v>1384</v>
+      </c>
+      <c r="L17">
+        <v>2816</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12">
       <c r="A18">
-        <v>2046</v>
+        <v>16</v>
       </c>
       <c r="B18">
-        <v>2046</v>
+        <v>15.99</v>
+      </c>
+      <c r="C18">
+        <v>756</v>
       </c>
       <c r="E18">
         <v>2</v>
@@ -913,13 +1037,25 @@
       <c r="I18">
         <v>2975</v>
       </c>
-    </row>
-    <row r="19" spans="1:9">
+      <c r="J18">
+        <v>2065</v>
+      </c>
+      <c r="K18">
+        <v>1160</v>
+      </c>
+      <c r="L18">
+        <v>2966</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12">
       <c r="A19">
-        <v>2046</v>
+        <v>20</v>
       </c>
       <c r="B19">
-        <v>2046</v>
+        <v>19.989999999999998</v>
+      </c>
+      <c r="C19">
+        <v>946</v>
       </c>
       <c r="E19">
         <v>3</v>
@@ -936,13 +1072,25 @@
       <c r="I19">
         <v>3381</v>
       </c>
-    </row>
-    <row r="20" spans="1:9">
+      <c r="J19">
+        <v>2064</v>
+      </c>
+      <c r="K19">
+        <v>755</v>
+      </c>
+      <c r="L19">
+        <v>3385</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12">
       <c r="A20">
-        <v>2046</v>
+        <v>24</v>
       </c>
       <c r="B20">
-        <v>2046</v>
+        <v>23.99</v>
+      </c>
+      <c r="C20">
+        <v>1135</v>
       </c>
       <c r="E20">
         <v>3.3</v>
@@ -959,13 +1107,25 @@
       <c r="I20">
         <v>3456</v>
       </c>
-    </row>
-    <row r="21" spans="1:9">
+      <c r="J20">
+        <v>2066</v>
+      </c>
+      <c r="K20">
+        <v>653</v>
+      </c>
+      <c r="L20">
+        <v>3496</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12">
       <c r="A21">
-        <v>2046</v>
+        <v>28</v>
       </c>
       <c r="B21">
-        <v>2046</v>
+        <v>27.98</v>
+      </c>
+      <c r="C21">
+        <v>1325</v>
       </c>
       <c r="E21">
         <v>4</v>
@@ -982,13 +1142,25 @@
       <c r="I21">
         <v>3807</v>
       </c>
-    </row>
-    <row r="22" spans="1:9">
+      <c r="J21">
+        <v>2064</v>
+      </c>
+      <c r="K21">
+        <v>383</v>
+      </c>
+      <c r="L21">
+        <v>3776</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12">
       <c r="A22">
-        <v>2046</v>
+        <v>31</v>
       </c>
       <c r="B22">
-        <v>2046</v>
+        <v>30.98</v>
+      </c>
+      <c r="C22">
+        <v>1468</v>
       </c>
       <c r="E22">
         <v>4.25</v>
@@ -1004,6 +1176,59 @@
       </c>
       <c r="I22">
         <v>3879</v>
+      </c>
+      <c r="J22">
+        <v>2066</v>
+      </c>
+      <c r="K22">
+        <v>276</v>
+      </c>
+      <c r="L22">
+        <v>3853</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12">
+      <c r="A23">
+        <v>40</v>
+      </c>
+      <c r="B23">
+        <v>39.979999999999997</v>
+      </c>
+      <c r="C23">
+        <v>1897</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12">
+      <c r="A24">
+        <v>50</v>
+      </c>
+      <c r="B24">
+        <v>49.97</v>
+      </c>
+      <c r="C24">
+        <v>2374</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12">
+      <c r="A25">
+        <v>60</v>
+      </c>
+      <c r="B25">
+        <v>59.97</v>
+      </c>
+      <c r="C25">
+        <v>2852</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12">
+      <c r="A26">
+        <v>62</v>
+      </c>
+      <c r="B26">
+        <v>61.97</v>
+      </c>
+      <c r="C26">
+        <v>2945</v>
       </c>
     </row>
   </sheetData>
